--- a/fliad-plugin/plugin-hikvision/model/hikvision.orm.xlsx
+++ b/fliad-plugin/plugin-hikvision/model/hikvision.orm.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="211">
   <si>
     <t>序号</t>
   </si>
@@ -460,7 +460,10 @@
     <t>IDX_HIKVISION_CAMERA_NAME</t>
   </si>
   <si>
-    <t>name</t>
+    <t>IDX_HIKVISION_CAMERA_IP_ADDR</t>
+  </si>
+  <si>
+    <t>IDX_HIKVISION_CAMERA_DEVICE_ID</t>
   </si>
   <si>
     <t>别名列表</t>
@@ -2683,12 +2686,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="4.33333333333333" customWidth="1"/>
     <col min="2" max="2" width="4.41666666666667" customWidth="1"/>
-    <col min="3" max="3" width="16.9166666666667" customWidth="1"/>
+    <col min="3" max="3" width="25.75" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="4.66666666666667" customWidth="1"/>
     <col min="6" max="6" width="4.75" customWidth="1"/>
@@ -3604,7 +3607,7 @@
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -3623,84 +3626,140 @@
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
     </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="3">
+        <v>2</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+    </row>
     <row r="37" spans="1:18">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="3">
+        <v>3</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="8"/>
-    </row>
-    <row r="38" spans="1:18">
-      <c r="A38" s="1" t="s">
+      <c r="C37" s="3"/>
+      <c r="D37" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8"/>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1" t="s">
+      <c r="J40" s="1"/>
+      <c r="K40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-    </row>
-    <row r="39" spans="1:18">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="R39" s="9"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
+  <mergeCells count="80">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="J1:O1"/>
@@ -3761,17 +3820,25 @@
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="I35:L35"/>
     <mergeCell ref="M35:R35"/>
-    <mergeCell ref="A37:R37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:R38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:R39"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="M36:R36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:R37"/>
+    <mergeCell ref="A39:R39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="M40:R40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="M41:R41"/>
     <mergeCell ref="A23:A30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3795,7 +3862,7 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -3805,7 +3872,7 @@
         <v>76</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -3823,7 +3890,7 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -4029,13 +4096,13 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="3"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -4063,13 +4130,13 @@
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="3"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -4097,13 +4164,13 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="3"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -4131,13 +4198,13 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="3"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
@@ -4163,13 +4230,13 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="3"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
@@ -4197,13 +4264,13 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="3"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
@@ -4231,13 +4298,13 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="3"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
@@ -4265,13 +4332,13 @@
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="3"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
@@ -4297,13 +4364,13 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="3"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -4331,13 +4398,13 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="3"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
@@ -4365,13 +4432,13 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="3"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
@@ -4397,13 +4464,13 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="3"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
@@ -4431,13 +4498,13 @@
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="3"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
@@ -4465,13 +4532,13 @@
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="3"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
@@ -4499,13 +4566,13 @@
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="3"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
@@ -4533,13 +4600,13 @@
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="3"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
@@ -4565,13 +4632,13 @@
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="3"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
@@ -4599,13 +4666,13 @@
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="3"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
@@ -4631,13 +4698,13 @@
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="3"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
@@ -4663,13 +4730,13 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E28" s="9"/>
       <c r="F28" s="3"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
@@ -4697,13 +4764,13 @@
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="3"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
@@ -4731,13 +4798,13 @@
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E30" s="9"/>
       <c r="F30" s="3"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
@@ -4765,13 +4832,13 @@
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E31" s="9"/>
       <c r="F31" s="3"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -4799,13 +4866,13 @@
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E32" s="9"/>
       <c r="F32" s="3"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
@@ -4833,13 +4900,13 @@
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="3"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="9"/>
@@ -4867,13 +4934,13 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="3"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
@@ -4901,13 +4968,13 @@
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="3"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
@@ -4933,13 +5000,13 @@
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="3"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
@@ -4967,13 +5034,13 @@
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E37" s="9"/>
       <c r="F37" s="3"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
@@ -4999,13 +5066,13 @@
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E38" s="9"/>
       <c r="F38" s="3"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -5033,13 +5100,13 @@
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E39" s="9"/>
       <c r="F39" s="3"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
@@ -5394,7 +5461,7 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -5423,7 +5490,7 @@
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>

--- a/fliad-plugin/plugin-hikvision/model/hikvision.orm.xlsx
+++ b/fliad-plugin/plugin-hikvision/model/hikvision.orm.xlsx
@@ -1437,7 +1437,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1512,6 +1512,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1927,7 +1930,7 @@
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
+      <c r="B2" s="48"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
     </row>
@@ -1935,7 +1938,7 @@
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="47"/>
+      <c r="B3" s="48"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
     </row>
@@ -2007,7 +2010,7 @@
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="45" t="b">
+      <c r="B2" s="46" t="b">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -2018,7 +2021,7 @@
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="47" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -2029,7 +2032,7 @@
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="47" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -2040,7 +2043,7 @@
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="47" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2051,7 +2054,7 @@
       <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="47" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -2062,7 +2065,7 @@
       <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="47" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -2073,7 +2076,7 @@
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="47" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -2084,7 +2087,7 @@
       <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="47" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -2095,7 +2098,7 @@
       <c r="A10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="47" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -2157,379 +2160,379 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="42" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="42">
+      <c r="A2" s="43">
         <v>1</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43" t="s">
+      <c r="C2" s="44"/>
+      <c r="D2" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="43">
+      <c r="E2" s="44">
         <v>50</v>
       </c>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="42">
+      <c r="A3" s="43">
         <v>2</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43" t="s">
+      <c r="C3" s="44"/>
+      <c r="D3" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="44">
         <v>100</v>
       </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="42">
+      <c r="A4" s="43">
         <v>3</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43" t="s">
+      <c r="C4" s="44"/>
+      <c r="D4" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="43">
+      <c r="E4" s="44">
         <v>100</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="42">
+      <c r="A5" s="43">
         <v>4</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43" t="s">
+      <c r="C5" s="44"/>
+      <c r="D5" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="44">
         <v>100</v>
       </c>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="42">
+      <c r="A6" s="43">
         <v>5</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43" t="s">
+      <c r="C6" s="44"/>
+      <c r="D6" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="44">
         <v>100</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="42">
+      <c r="A7" s="43">
         <v>6</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43" t="s">
+      <c r="C7" s="44"/>
+      <c r="D7" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="44">
         <v>50</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="42">
+      <c r="A8" s="43">
         <v>7</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43" t="s">
+      <c r="C8" s="44"/>
+      <c r="D8" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="44">
         <v>50</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="42">
+      <c r="A9" s="43">
         <v>8</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43" t="s">
+      <c r="C9" s="44"/>
+      <c r="D9" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="42">
+      <c r="A10" s="43">
         <v>9</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="42">
+      <c r="A11" s="43">
         <v>10</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43" t="s">
+      <c r="C11" s="44"/>
+      <c r="D11" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="44">
         <v>1</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="42">
+      <c r="A12" s="43">
         <v>11</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43" t="s">
+      <c r="C12" s="44"/>
+      <c r="D12" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="42">
+      <c r="A13" s="43">
         <v>12</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43" t="s">
+      <c r="C13" s="44"/>
+      <c r="D13" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="42">
+      <c r="A14" s="43">
         <v>13</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="44">
         <v>50</v>
       </c>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="42">
+      <c r="A15" s="43">
         <v>14</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="42">
+      <c r="A16" s="43">
         <v>15</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43" t="s">
+      <c r="C16" s="44"/>
+      <c r="D16" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="44">
         <v>50</v>
       </c>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="42">
+      <c r="A17" s="43">
         <v>16</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43" t="s">
+      <c r="C17" s="44"/>
+      <c r="D17" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="42">
+      <c r="A18" s="43">
         <v>17</v>
       </c>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43" t="s">
+      <c r="C18" s="44"/>
+      <c r="D18" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="45">
         <v>16777215</v>
       </c>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="42">
+      <c r="A19" s="43">
         <v>18</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43" t="s">
+      <c r="C19" s="44"/>
+      <c r="D19" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="43">
+      <c r="E19" s="44">
         <v>200</v>
       </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="43"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="43"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="43"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="43"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="43"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2551,84 +2554,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="25">
+      <c r="A1" s="26">
         <v>1</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="26" t="s">
+      <c r="E1" s="30"/>
+      <c r="F1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="30" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="30"/>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="28" t="s">
+      <c r="C2" s="28"/>
+      <c r="D2" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="26" t="s">
+      <c r="E2" s="30"/>
+      <c r="F2" s="27" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="30"/>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="31"/>
+      <c r="B3" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="29"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="30"/>
-      <c r="B4" s="32" t="s">
+      <c r="A4" s="31"/>
+      <c r="B4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="35"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="30"/>
-      <c r="B5" s="35" t="s">
+      <c r="A5" s="31"/>
+      <c r="B5" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="37" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="3">
         <v>1</v>
       </c>
@@ -2643,7 +2646,7 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" ht="13.5" customHeight="1" spans="1:7">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="3">
         <v>2</v>
       </c>
@@ -2658,12 +2661,12 @@
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="37"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="13"/>
     </row>
   </sheetData>
@@ -3164,10 +3167,10 @@
       <c r="K15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="L15" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="L15" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="25">
         <v>1</v>
       </c>
       <c r="N15" s="3"/>
@@ -3202,10 +3205,10 @@
       <c r="K16" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="L16" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="M16" s="3">
+      <c r="L16" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="25">
         <v>1</v>
       </c>
       <c r="N16" s="3"/>
